--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9652B932-DC59-4B72-82C8-B9995D83C24C}"/>
+  <xr:revisionPtr revIDLastSave="298" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50AC3144-BEAE-4CF1-864E-6D1124C823B4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="136">
   <si>
     <t>Date</t>
   </si>
@@ -414,9 +414,6 @@
     <t>What is the functional modules will be generated after activating the lock object?</t>
   </si>
   <si>
-    <t>Practice whatever taught in today's session.</t>
-  </si>
-  <si>
     <t>Do R&amp;D on row level lockin and work on it.</t>
   </si>
   <si>
@@ -429,22 +426,22 @@
     <t>Difference between Type and Data ?</t>
   </si>
   <si>
-    <t> What is Local Structure and Global Structure ?</t>
-  </si>
-  <si>
     <t>What is Flat structure and nested structure and create flat and nested struct in the reports ?</t>
   </si>
   <si>
-    <t> Create  Deep structure , DO R&amp;D  ?</t>
-  </si>
-  <si>
     <t>create  a nested structure with 8 fields without using global structure and assign the value To all the fields in the structure  and print them in  output  screen ?</t>
   </si>
   <si>
-    <t> Difference between work area and Internal table</t>
-  </si>
-  <si>
     <t>How many ways we can create reports program</t>
+  </si>
+  <si>
+    <t>Difference between work area and Internal table</t>
+  </si>
+  <si>
+    <t>Create  Deep structure , DO R&amp;D  ?</t>
+  </si>
+  <si>
+    <t>What is Local Structure and Global Structure ?</t>
   </si>
 </sst>
 </file>
@@ -611,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -662,6 +659,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -678,10 +679,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -981,7 +978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:D146"/>
+  <dimension ref="A2:D144"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -1675,25 +1672,27 @@
         <v>126</v>
       </c>
     </row>
-    <row r="135" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B135" s="18" t="s">
+    <row r="135" spans="2:2" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.3">
+      <c r="B135" s="25"/>
+    </row>
+    <row r="136" spans="2:2" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B136" s="23" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="136" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B136" s="18"/>
-    </row>
-    <row r="137" spans="2:2" ht="18" x14ac:dyDescent="0.3">
-      <c r="B137" s="18"/>
-    </row>
-    <row r="138" spans="2:2" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B138" s="23" t="s">
+    <row r="137" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="B137" s="21" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
+      <c r="B138" s="21" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="139" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B139" s="21" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
@@ -1703,12 +1702,12 @@
     </row>
     <row r="141" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B141" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B142" s="22" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="B142" s="21" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="143" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
@@ -1718,17 +1717,7 @@
     </row>
     <row r="144" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B144" s="22" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="B145" s="21" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2" ht="18" x14ac:dyDescent="0.35">
-      <c r="B146" s="22" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="298" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50AC3144-BEAE-4CF1-864E-6D1124C823B4}"/>
+  <xr:revisionPtr revIDLastSave="320" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01396F31-65E2-420B-8355-0A00961C912E}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="150">
   <si>
     <t>Date</t>
   </si>
@@ -442,13 +442,55 @@
   </si>
   <si>
     <t>What is Local Structure and Global Structure ?</t>
+  </si>
+  <si>
+    <t>Assignment-17 -   internal tables</t>
+  </si>
+  <si>
+    <t>Create a standard internal table, fill the values and display them</t>
+  </si>
+  <si>
+    <t>Create a standard internal table, fill the values, refresh it and again display the values</t>
+  </si>
+  <si>
+    <t>Create a sorted internal table, fill the values and display them</t>
+  </si>
+  <si>
+    <t>create a hashed internal table, fill the values and display them</t>
+  </si>
+  <si>
+    <t>Transfer the data from one internal table to another internal table</t>
+  </si>
+  <si>
+    <t>Create any internal, fill the values and read data without and with binary search.</t>
+  </si>
+  <si>
+    <t>Create a internal table, fill the values. read the data based on condition and modify the read record (R&amp;D) question</t>
+  </si>
+  <si>
+    <t>Assignment 17</t>
+  </si>
+  <si>
+    <t>ZKR_RP_INTERNAL_TABLE1</t>
+  </si>
+  <si>
+    <t>ZKR_RP_INTERNAL_TABLE_TRANSFER</t>
+  </si>
+  <si>
+    <t>ZKR_RP_STANDART_INTERNAL_TABLE</t>
+  </si>
+  <si>
+    <t>ZKR_RP_SORTED_INTERNAL_TABLE</t>
+  </si>
+  <si>
+    <t>ZKR_RP_HASHED_INTERNAL_TABLE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,6 +616,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF242424"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -608,7 +658,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -659,10 +709,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -679,6 +726,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -978,13 +1029,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:D144"/>
+  <dimension ref="A2:D153"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="122.44140625" customWidth="1"/>
     <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="31.44140625" customWidth="1"/>
+    <col min="4" max="4" width="34.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -1672,8 +1723,8 @@
         <v>126</v>
       </c>
     </row>
-    <row r="135" spans="2:2" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.3">
-      <c r="B135" s="25"/>
+    <row r="135" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B135" s="18"/>
     </row>
     <row r="136" spans="2:2" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B136" s="23" t="s">
@@ -1718,6 +1769,67 @@
     <row r="144" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B144" s="22" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B146" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B147" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D147" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B148" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D148" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B149" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="D149" s="17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B150" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="D150" s="17" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B151" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="D151" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B152" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D152" s="17" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B153" s="24" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1736,8 +1848,9 @@
     <hyperlink ref="C30" r:id="rId12" xr:uid="{554405B0-79E5-4112-A912-1BC501BF2F79}"/>
     <hyperlink ref="C100" r:id="rId13" xr:uid="{92ACD9A1-491A-4053-8C77-43C445256300}"/>
     <hyperlink ref="C109" r:id="rId14" xr:uid="{C2D5EE05-79ED-9942-B27E-2D0A9B97329B}"/>
+    <hyperlink ref="C146" r:id="rId15" xr:uid="{B42B48A7-BC3E-4A88-AB81-7D295A8A648C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId15"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="320" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01396F31-65E2-420B-8355-0A00961C912E}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44DFB830-0374-4826-BAE8-482D07B83707}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="154">
   <si>
     <t>Date</t>
   </si>
@@ -484,6 +484,18 @@
   </si>
   <si>
     <t>ZKR_RP_HASHED_INTERNAL_TABLE</t>
+  </si>
+  <si>
+    <t>Assignment 14</t>
+  </si>
+  <si>
+    <t>Assignment 15</t>
+  </si>
+  <si>
+    <t>Internal table operations and Syntax and which scenario we use.</t>
+  </si>
+  <si>
+    <t>Difference between Modify by Index and Transporting.</t>
   </si>
 </sst>
 </file>
@@ -1029,13 +1041,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:D153"/>
+  <dimension ref="A2:D156"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
     <col min="2" max="2" width="122.44140625" customWidth="1"/>
     <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="34.5546875" customWidth="1"/>
+    <col min="4" max="4" width="35.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.35">
@@ -1620,153 +1632,159 @@
         <v>105</v>
       </c>
     </row>
-    <row r="113" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B113" s="20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="114" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B114" s="20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="115" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B115" s="20" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="116" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B116" s="20" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="118" spans="2:2" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B118" s="6" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="119" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="C118" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B119" s="18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B120" s="18" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="121" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B121" s="18" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="122" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B122" s="18" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="123" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B123" s="18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="124" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B124" s="18" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="125" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B125" s="18" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="126" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B126" s="18" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="127" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B127" s="18" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="128" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B128" s="18"/>
     </row>
-    <row r="129" spans="2:2" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B129" s="6" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="130" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="C129" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B130" s="18" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="131" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B131" s="18" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="132" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B132" s="18" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="133" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B133" s="18" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="134" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B134" s="18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="135" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B135" s="18"/>
     </row>
-    <row r="136" spans="2:2" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B136" s="23" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="137" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B137" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="138" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B138" s="21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="139" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B139" s="21" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="140" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B140" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="141" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B141" s="21" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="142" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B142" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="143" spans="2:2" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B143" s="21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="144" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B144" s="22" t="s">
         <v>132</v>
       </c>
@@ -1830,6 +1848,16 @@
     <row r="153" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B153" s="24" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B155" s="20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B156" s="20" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -1849,8 +1877,10 @@
     <hyperlink ref="C100" r:id="rId13" xr:uid="{92ACD9A1-491A-4053-8C77-43C445256300}"/>
     <hyperlink ref="C109" r:id="rId14" xr:uid="{C2D5EE05-79ED-9942-B27E-2D0A9B97329B}"/>
     <hyperlink ref="C146" r:id="rId15" xr:uid="{B42B48A7-BC3E-4A88-AB81-7D295A8A648C}"/>
+    <hyperlink ref="C118" r:id="rId16" xr:uid="{1354ABF7-5F6F-4361-93F1-14088151F918}"/>
+    <hyperlink ref="C129" r:id="rId17" xr:uid="{BAE159BC-E831-4218-AC09-37FA91798630}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId16"/>
+  <pageSetup orientation="portrait" r:id="rId18"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="343" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44DFB830-0374-4826-BAE8-482D07B83707}"/>
+  <xr:revisionPtr revIDLastSave="396" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861333B9-22D7-4C95-8BC7-6DBEEB3BAC88}"/>
   <bookViews>
-    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="173">
   <si>
     <t>Date</t>
   </si>
@@ -471,9 +471,6 @@
     <t>Assignment 17</t>
   </si>
   <si>
-    <t>ZKR_RP_INTERNAL_TABLE1</t>
-  </si>
-  <si>
     <t>ZKR_RP_INTERNAL_TABLE_TRANSFER</t>
   </si>
   <si>
@@ -496,13 +493,73 @@
   </si>
   <si>
     <t>Difference between Modify by Index and Transporting.</t>
+  </si>
+  <si>
+    <t>Assignment-18 -   internal tables</t>
+  </si>
+  <si>
+    <t>What's the use of header line demonstrate with one program</t>
+  </si>
+  <si>
+    <t>How change the specific field value demonstrate with example</t>
+  </si>
+  <si>
+    <t>How to find 'n' no of records present inside Internal Table</t>
+  </si>
+  <si>
+    <t>For standard table both with &amp; without key field use clear statement &amp; check what'll happens to previous data &amp; Do</t>
+  </si>
+  <si>
+    <t>more R&amp;D on the same question</t>
+  </si>
+  <si>
+    <t>ZKR_RP_IT_BINARY_SEARCH</t>
+  </si>
+  <si>
+    <t>Assignment 16</t>
+  </si>
+  <si>
+    <t>primary key and secondary key with example.</t>
+  </si>
+  <si>
+    <t>IF ELSE Statements .</t>
+  </si>
+  <si>
+    <t>COND and Switch statements.</t>
+  </si>
+  <si>
+    <t>ZKR_RP_IT_HEADERLINE</t>
+  </si>
+  <si>
+    <t>ZKR_RP_INTERNAL_TABLE_MODIFY</t>
+  </si>
+  <si>
+    <t>Work on Collect statement, Adjacent Duplicate &amp; Deleting specific records from IT.</t>
+  </si>
+  <si>
+    <t>ZKR_RP_INTERNAL_TABLE_DELETE</t>
+  </si>
+  <si>
+    <t>Assignment-19 - control break statement</t>
+  </si>
+  <si>
+    <t>In "SPFLI" DBT take Condi, Period, City from, CharID , Cityto, Distance, Fltime &amp; print it's short description and also print particular carid distance &amp; fltime as explained in today's session</t>
+  </si>
+  <si>
+    <t>What is control break statement &amp; what are the statements we can use inside loop explain them</t>
+  </si>
+  <si>
+    <t>Different between At New &amp; On change</t>
+  </si>
+  <si>
+    <t>Assignment 18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,6 +693,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -670,7 +735,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -722,6 +787,15 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1041,11 +1115,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:D156"/>
+  <dimension ref="A2:D173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="122.44140625" customWidth="1"/>
+    <col min="2" max="2" width="124.109375" customWidth="1"/>
     <col min="3" max="3" width="28.33203125" customWidth="1"/>
     <col min="4" max="4" width="35.77734375" customWidth="1"/>
   </cols>
@@ -1657,7 +1731,7 @@
         <v>110</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="119" spans="2:3" ht="18" x14ac:dyDescent="0.3">
@@ -1713,7 +1787,7 @@
         <v>121</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="130" spans="2:3" ht="18" x14ac:dyDescent="0.3">
@@ -1748,6 +1822,9 @@
       <c r="B136" s="23" t="s">
         <v>127</v>
       </c>
+      <c r="C136" s="8" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="137" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
       <c r="B137" s="21" t="s">
@@ -1802,7 +1879,7 @@
         <v>137</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="2:4" ht="18" x14ac:dyDescent="0.35">
@@ -1810,7 +1887,7 @@
         <v>138</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="2:4" ht="18" x14ac:dyDescent="0.35">
@@ -1818,7 +1895,7 @@
         <v>139</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="150" spans="2:4" ht="18" x14ac:dyDescent="0.35">
@@ -1826,7 +1903,7 @@
         <v>140</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="151" spans="2:4" ht="18" x14ac:dyDescent="0.35">
@@ -1834,7 +1911,7 @@
         <v>141</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="152" spans="2:4" ht="18" x14ac:dyDescent="0.35">
@@ -1842,7 +1919,7 @@
         <v>142</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
     </row>
     <row r="153" spans="2:4" ht="18" x14ac:dyDescent="0.35">
@@ -1852,12 +1929,97 @@
     </row>
     <row r="155" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B155" s="20" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="156" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B156" s="20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B158" s="27" t="s">
         <v>153</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B159" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D159" s="17" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B160" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D160" s="17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B161" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D161" s="17" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B162" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="D162" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B163" s="26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B164" s="24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B166" s="20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B167" s="28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B168" s="20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B170" s="29" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B171" s="26" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B172" s="26" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B173" s="26" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -1879,8 +2041,10 @@
     <hyperlink ref="C146" r:id="rId15" xr:uid="{B42B48A7-BC3E-4A88-AB81-7D295A8A648C}"/>
     <hyperlink ref="C118" r:id="rId16" xr:uid="{1354ABF7-5F6F-4361-93F1-14088151F918}"/>
     <hyperlink ref="C129" r:id="rId17" xr:uid="{BAE159BC-E831-4218-AC09-37FA91798630}"/>
+    <hyperlink ref="C136" r:id="rId18" xr:uid="{67E94C95-D601-4AA0-886F-A8E78BE961BC}"/>
+    <hyperlink ref="C158" r:id="rId19" xr:uid="{E3BAF59C-C59B-4D8D-9602-4AC070513FE4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId18"/>
+  <pageSetup orientation="portrait" r:id="rId20"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="396" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861333B9-22D7-4C95-8BC7-6DBEEB3BAC88}"/>
+  <xr:revisionPtr revIDLastSave="418" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76F48ED2-EA80-494C-A2E8-E83812C0AB51}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="174">
   <si>
     <t>Date</t>
   </si>
@@ -552,7 +552,10 @@
     <t>Different between At New &amp; On change</t>
   </si>
   <si>
-    <t>Assignment 18</t>
+    <t xml:space="preserve"> Assignment 18</t>
+  </si>
+  <si>
+    <t>Assignment 19</t>
   </si>
 </sst>
 </file>
@@ -795,7 +798,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1115,11 +1118,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:D173"/>
+  <dimension ref="A2:E173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="124.109375" customWidth="1"/>
+    <col min="2" max="2" width="147.33203125" customWidth="1"/>
     <col min="3" max="3" width="28.33203125" customWidth="1"/>
     <col min="4" max="4" width="35.77734375" customWidth="1"/>
   </cols>
@@ -1961,7 +1964,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="161" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="161" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B161" s="25" t="s">
         <v>156</v>
       </c>
@@ -1969,7 +1972,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="162" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="162" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B162" s="25" t="s">
         <v>166</v>
       </c>
@@ -1977,50 +1980,56 @@
         <v>167</v>
       </c>
     </row>
-    <row r="163" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="163" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B163" s="26" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="164" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="164" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B164" s="24" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="166" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="166" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B166" s="20" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="167" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="167" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B167" s="28" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="168" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="168" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B168" s="20" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="170" spans="2:4" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:5" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B170" s="29" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="171" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="C170" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B171" s="26" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="172" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="172" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B172" s="26" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="173" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+    <row r="173" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B173" s="26" t="s">
         <v>169</v>
       </c>
+      <c r="C173" s="26"/>
+      <c r="D173" s="26"/>
+      <c r="E173" s="26"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2043,8 +2052,9 @@
     <hyperlink ref="C129" r:id="rId17" xr:uid="{BAE159BC-E831-4218-AC09-37FA91798630}"/>
     <hyperlink ref="C136" r:id="rId18" xr:uid="{67E94C95-D601-4AA0-886F-A8E78BE961BC}"/>
     <hyperlink ref="C158" r:id="rId19" xr:uid="{E3BAF59C-C59B-4D8D-9602-4AC070513FE4}"/>
+    <hyperlink ref="C170" r:id="rId20" xr:uid="{BD960CC7-81C9-44EF-875E-558B0E643B6E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId20"/>
+  <pageSetup orientation="portrait" r:id="rId21"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76F48ED2-EA80-494C-A2E8-E83812C0AB51}"/>
+  <xr:revisionPtr revIDLastSave="464" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A142CB29-52E2-4459-864B-E5DDFFE71B8F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="202">
   <si>
     <t>Date</t>
   </si>
@@ -556,13 +556,109 @@
   </si>
   <si>
     <t>Assignment 19</t>
+  </si>
+  <si>
+    <t>Assignment-20 - debugging</t>
+  </si>
+  <si>
+    <t>1.what is debugging and types of debuggers in sap</t>
+  </si>
+  <si>
+    <t>2.Difference between Static and Dynamic Breakpoint</t>
+  </si>
+  <si>
+    <t>3.Difference between Classical and New Debugger</t>
+  </si>
+  <si>
+    <t>4.What is the Use of function key F5, F6, F7, f8, shift +F8, shift+ F12</t>
+  </si>
+  <si>
+    <t>5.How we can change internal table data in debugging</t>
+  </si>
+  <si>
+    <t>Assignment21 - debugging</t>
+  </si>
+  <si>
+    <t>1. What is breakpoints and What are the types of breakpoints explore more on it?</t>
+  </si>
+  <si>
+    <t>2. What is watchpoint ? How to create watchpoint?</t>
+  </si>
+  <si>
+    <t>3. Create report program in that create watch point for variable and explore more on it?</t>
+  </si>
+  <si>
+    <t>4. Explore on all tabs in debugging tool?</t>
+  </si>
+  <si>
+    <t>5. Difference between Breakpoints and Watchpoints?</t>
+  </si>
+  <si>
+    <t>Assignment-22 - select statement</t>
+  </si>
+  <si>
+    <t>1. Difference between select single and select up to 1 row</t>
+  </si>
+  <si>
+    <r>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Disadvantages of inner join and Advantages of for all entries?</t>
+    </r>
+  </si>
+  <si>
+    <t>3. practice select query using 3 table and using inner join?</t>
+  </si>
+  <si>
+    <t>4. practice select query using 3 table using for all entries?</t>
+  </si>
+  <si>
+    <t>5. Practice whatever taught in session on select single and select upto 1 row?</t>
+  </si>
+  <si>
+    <t>6. Retrieve Specific Data and Retrieve single record based on given input from sales order header?</t>
+  </si>
+  <si>
+    <t>Assignment-23-  select statement using joins</t>
+  </si>
+  <si>
+    <t>1. Retrieve data from purchase order header table and item table to create purchase order by inner join</t>
+  </si>
+  <si>
+    <t>2. Retrieve data from purchase order header table and item table to create purchase order by for all entries?</t>
+  </si>
+  <si>
+    <t>3. Retrieve data from purchase order header table and item table to create purchase order by parallel curser techAQ1?</t>
+  </si>
+  <si>
+    <t>4. Explore on the exact difference between all of the above techniques?</t>
+  </si>
+  <si>
+    <t>Assignment 22</t>
+  </si>
+  <si>
+    <t>Assignment 23</t>
+  </si>
+  <si>
+    <t>Assignment 20</t>
+  </si>
+  <si>
+    <t>Assignment 21</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -704,8 +800,44 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF242424"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="16"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -724,6 +856,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -738,7 +876,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -799,6 +937,26 @@
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1118,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E173"/>
+  <dimension ref="A2:E204"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -2030,6 +2188,141 @@
       <c r="C173" s="26"/>
       <c r="D173" s="26"/>
       <c r="E173" s="26"/>
+    </row>
+    <row r="175" spans="2:5" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B175" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B176" s="30" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B177" s="30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B178" s="30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B179" s="30" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B180" s="38" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B182" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="183" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B183" s="31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B184" s="36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B185" s="36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B186" s="36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B187" s="36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B189" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B190" s="30" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B191" s="32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B192" s="33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B193" s="30" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B194" s="30" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B195" s="30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B197" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B198" s="35" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B199" s="35" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B200" s="37" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B201" s="30" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" ht="21" x14ac:dyDescent="0.4">
+      <c r="C204" s="39"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2053,8 +2346,12 @@
     <hyperlink ref="C136" r:id="rId18" xr:uid="{67E94C95-D601-4AA0-886F-A8E78BE961BC}"/>
     <hyperlink ref="C158" r:id="rId19" xr:uid="{E3BAF59C-C59B-4D8D-9602-4AC070513FE4}"/>
     <hyperlink ref="C170" r:id="rId20" xr:uid="{BD960CC7-81C9-44EF-875E-558B0E643B6E}"/>
+    <hyperlink ref="C189" r:id="rId21" xr:uid="{1CA56D93-28F4-42FF-B31C-374CBB719CA0}"/>
+    <hyperlink ref="C197" r:id="rId22" xr:uid="{5255945A-DC3C-4B88-9302-30F148716776}"/>
+    <hyperlink ref="C175" r:id="rId23" xr:uid="{3B828FF7-9778-4245-89C6-39A3C01482FA}"/>
+    <hyperlink ref="C182" r:id="rId24" xr:uid="{F4F4C03C-5982-4E12-A7D9-612B9828C231}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId21"/>
+  <pageSetup orientation="portrait" r:id="rId25"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="464" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A142CB29-52E2-4459-864B-E5DDFFE71B8F}"/>
+  <xr:revisionPtr revIDLastSave="506" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5642B141-BB2E-413D-8390-1B31684DD761}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="232">
   <si>
     <t>Date</t>
   </si>
@@ -652,6 +652,108 @@
   </si>
   <si>
     <t>Assignment 21</t>
+  </si>
+  <si>
+    <t>Assignment-24 - debugging</t>
+  </si>
+  <si>
+    <t>1.How many watch points can be created?</t>
+  </si>
+  <si>
+    <t>2.How to add your data from desktop to your internal table in debugging?</t>
+  </si>
+  <si>
+    <t>3.How to check write statements in debugging?</t>
+  </si>
+  <si>
+    <t>5.How to compare variables inside debugging?</t>
+  </si>
+  <si>
+    <t>6.What are the function keys used in debugging?</t>
+  </si>
+  <si>
+    <t>7.Difference between Breakpoints and Watchpoints?</t>
+  </si>
+  <si>
+    <t>Assignment-25 - aggrigate function</t>
+  </si>
+  <si>
+    <t>1.What are aggregate functions and its use?</t>
+  </si>
+  <si>
+    <t>2.what are the types of aggregate functions and explain?</t>
+  </si>
+  <si>
+    <t>3.Create all types of aggregate functions using a custom table?</t>
+  </si>
+  <si>
+    <t>4.which data types are not used in aggregate functions?</t>
+  </si>
+  <si>
+    <t>5.Create a program by adding all aggregate functions in single select statement using any standard data base table?</t>
+  </si>
+  <si>
+    <t>Assignment-26 - inline declaration</t>
+  </si>
+  <si>
+    <t>1. Retrieve data from sales order header (VBAK) &amp; item (VBAP) by for all entries &amp; use inline declaration?</t>
+  </si>
+  <si>
+    <t>2. Check all select statement by inline declaration?</t>
+  </si>
+  <si>
+    <r>
+      <t>3. Diff b/w left outer &amp; right outer join with practically by using purchase order header (EKKO) &amp; item (EKPO) table</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Assignment-27 - field symbol</t>
+  </si>
+  <si>
+    <t>1.What is Filed symbol ? types of field symbols?</t>
+  </si>
+  <si>
+    <t>2.Difference between Work area and field  Symbol?</t>
+  </si>
+  <si>
+    <t>3.Fetch 100 records from mara and change material type  'FERT'  to  'FT'  and  'SERV '  to  'SE'  and display them in table formate (Dont use work area in program use  typed field symbols).</t>
+  </si>
+  <si>
+    <t>4. Fetch 100 records from sales order header and change sales doc to '0000000001' for seles doc '0000018341'  and  '0000018345' and display them in table formate (Dont use work area in program use  typed field symbols).</t>
+  </si>
+  <si>
+    <t>5.Use Parallel curser with field symbol</t>
+  </si>
+  <si>
+    <t>ZKR_RP_PC_FS</t>
+  </si>
+  <si>
+    <t>Assignment 27</t>
+  </si>
+  <si>
+    <t>4.How we can change internal table data in debugging?(refer assignment 20 5th question)</t>
+  </si>
+  <si>
+    <t>8.How many external breakpoints is possible in session?</t>
+  </si>
+  <si>
+    <t>9. How to deactivate breakpoint in runtime and how to delete breakpoint at runtime?</t>
+  </si>
+  <si>
+    <t>10.What is the use stack?</t>
+  </si>
+  <si>
+    <t>Assignment 24</t>
   </si>
 </sst>
 </file>
@@ -829,15 +931,13 @@
     </font>
     <font>
       <b/>
-      <u/>
-      <sz val="16"/>
-      <color theme="10"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -856,12 +956,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -876,7 +970,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -946,16 +1040,6 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1276,7 +1360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E204"/>
+  <dimension ref="A2:E234"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -2218,7 +2302,7 @@
       </c>
     </row>
     <row r="180" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B180" s="38" t="s">
+      <c r="B180" s="30" t="s">
         <v>179</v>
       </c>
     </row>
@@ -2236,22 +2320,22 @@
       </c>
     </row>
     <row r="184" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B184" s="36" t="s">
+      <c r="B184" s="31" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="185" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B185" s="36" t="s">
+      <c r="B185" s="31" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="186" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B186" s="36" t="s">
+      <c r="B186" s="31" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="187" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B187" s="36" t="s">
+      <c r="B187" s="31" t="s">
         <v>185</v>
       </c>
     </row>
@@ -2312,7 +2396,7 @@
       </c>
     </row>
     <row r="200" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B200" s="37" t="s">
+      <c r="B200" s="35" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2321,8 +2405,158 @@
         <v>197</v>
       </c>
     </row>
-    <row r="204" spans="2:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="C204" s="39"/>
+    <row r="204" spans="2:3" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B204" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="C204" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B205" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B206" s="30" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B207" s="30" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B208" s="30" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B209" s="30" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B210" s="30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B211" s="30" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B212" s="30" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B213" s="30" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B214" s="30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B216" s="34" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B217" s="30" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B218" s="30" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B219" s="30" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B220" s="30" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B221" s="30" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B222" s="30"/>
+    </row>
+    <row r="223" spans="2:2" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B223" s="34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B224" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B225" s="33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B226" s="33" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B227" s="33"/>
+    </row>
+    <row r="228" spans="2:4" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B228" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C228" s="8" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B229" s="30" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B230" s="30" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B231" s="30" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B232" s="30" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B233" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="D233" s="17" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B234" s="30"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2350,8 +2584,10 @@
     <hyperlink ref="C197" r:id="rId22" xr:uid="{5255945A-DC3C-4B88-9302-30F148716776}"/>
     <hyperlink ref="C175" r:id="rId23" xr:uid="{3B828FF7-9778-4245-89C6-39A3C01482FA}"/>
     <hyperlink ref="C182" r:id="rId24" xr:uid="{F4F4C03C-5982-4E12-A7D9-612B9828C231}"/>
+    <hyperlink ref="C228" r:id="rId25" xr:uid="{2277D97B-A360-4242-8244-55BB1729762C}"/>
+    <hyperlink ref="C204" r:id="rId26" xr:uid="{1AEE8A7C-CF6E-49EC-AFFD-4E0A8D389E0B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId25"/>
+  <pageSetup orientation="portrait" r:id="rId27"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="506" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5642B141-BB2E-413D-8390-1B31684DD761}"/>
+  <xr:revisionPtr revIDLastSave="510" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C673EB-ACFE-4CB4-93DA-35F80C8CD221}"/>
   <bookViews>
     <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="237">
   <si>
     <t>Date</t>
   </si>
@@ -598,6 +598,144 @@
   </si>
   <si>
     <t>1. Difference between select single and select up to 1 row</t>
+  </si>
+  <si>
+    <t>3. practice select query using 3 table and using inner join?</t>
+  </si>
+  <si>
+    <t>4. practice select query using 3 table using for all entries?</t>
+  </si>
+  <si>
+    <t>5. Practice whatever taught in session on select single and select upto 1 row?</t>
+  </si>
+  <si>
+    <t>6. Retrieve Specific Data and Retrieve single record based on given input from sales order header?</t>
+  </si>
+  <si>
+    <t>Assignment-23-  select statement using joins</t>
+  </si>
+  <si>
+    <t>1. Retrieve data from purchase order header table and item table to create purchase order by inner join</t>
+  </si>
+  <si>
+    <t>2. Retrieve data from purchase order header table and item table to create purchase order by for all entries?</t>
+  </si>
+  <si>
+    <t>3. Retrieve data from purchase order header table and item table to create purchase order by parallel curser techAQ1?</t>
+  </si>
+  <si>
+    <t>4. Explore on the exact difference between all of the above techniques?</t>
+  </si>
+  <si>
+    <t>Assignment 22</t>
+  </si>
+  <si>
+    <t>Assignment 23</t>
+  </si>
+  <si>
+    <t>Assignment 20</t>
+  </si>
+  <si>
+    <t>Assignment 21</t>
+  </si>
+  <si>
+    <t>Assignment-24 - debugging</t>
+  </si>
+  <si>
+    <t>1.How many watch points can be created?</t>
+  </si>
+  <si>
+    <t>2.How to add your data from desktop to your internal table in debugging?</t>
+  </si>
+  <si>
+    <t>3.How to check write statements in debugging?</t>
+  </si>
+  <si>
+    <t>5.How to compare variables inside debugging?</t>
+  </si>
+  <si>
+    <t>6.What are the function keys used in debugging?</t>
+  </si>
+  <si>
+    <t>7.Difference between Breakpoints and Watchpoints?</t>
+  </si>
+  <si>
+    <t>Assignment-25 - aggrigate function</t>
+  </si>
+  <si>
+    <t>1.What are aggregate functions and its use?</t>
+  </si>
+  <si>
+    <t>2.what are the types of aggregate functions and explain?</t>
+  </si>
+  <si>
+    <t>3.Create all types of aggregate functions using a custom table?</t>
+  </si>
+  <si>
+    <t>4.which data types are not used in aggregate functions?</t>
+  </si>
+  <si>
+    <t>5.Create a program by adding all aggregate functions in single select statement using any standard data base table?</t>
+  </si>
+  <si>
+    <t>Assignment-26 - inline declaration</t>
+  </si>
+  <si>
+    <t>1. Retrieve data from sales order header (VBAK) &amp; item (VBAP) by for all entries &amp; use inline declaration?</t>
+  </si>
+  <si>
+    <t>2. Check all select statement by inline declaration?</t>
+  </si>
+  <si>
+    <t>Assignment-27 - field symbol</t>
+  </si>
+  <si>
+    <t>1.What is Filed symbol ? types of field symbols?</t>
+  </si>
+  <si>
+    <t>2.Difference between Work area and field  Symbol?</t>
+  </si>
+  <si>
+    <t>3.Fetch 100 records from mara and change material type  'FERT'  to  'FT'  and  'SERV '  to  'SE'  and display them in table formate (Dont use work area in program use  typed field symbols).</t>
+  </si>
+  <si>
+    <t>4. Fetch 100 records from sales order header and change sales doc to '0000000001' for seles doc '0000018341'  and  '0000018345' and display them in table formate (Dont use work area in program use  typed field symbols).</t>
+  </si>
+  <si>
+    <t>5.Use Parallel curser with field symbol</t>
+  </si>
+  <si>
+    <t>ZKR_RP_PC_FS</t>
+  </si>
+  <si>
+    <t>Assignment 27</t>
+  </si>
+  <si>
+    <t>8.How many external breakpoints is possible in session?</t>
+  </si>
+  <si>
+    <t>9. How to deactivate breakpoint in runtime and how to delete breakpoint at runtime?</t>
+  </si>
+  <si>
+    <t>10.What is the use stack?</t>
+  </si>
+  <si>
+    <t>Assignment 24</t>
+  </si>
+  <si>
+    <t>Assignment-28 - field symbol</t>
+  </si>
+  <si>
+    <t>1.Retrive data from purchase order header table and try to access by field symbol?</t>
+  </si>
+  <si>
+    <t>2.Modify  internal table field without FS and with FS?</t>
+  </si>
+  <si>
+    <t>3.Perform any operation and calculate time required for both ( Without FS and with FS)?</t>
+  </si>
+  <si>
+    <t>4.Practice on Typed field symbol and generic Field symbol?</t>
   </si>
   <si>
     <r>
@@ -608,98 +746,12 @@
         <b/>
         <sz val="14"/>
         <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Disadvantages of inner join and Advantages of for all entries?</t>
     </r>
-  </si>
-  <si>
-    <t>3. practice select query using 3 table and using inner join?</t>
-  </si>
-  <si>
-    <t>4. practice select query using 3 table using for all entries?</t>
-  </si>
-  <si>
-    <t>5. Practice whatever taught in session on select single and select upto 1 row?</t>
-  </si>
-  <si>
-    <t>6. Retrieve Specific Data and Retrieve single record based on given input from sales order header?</t>
-  </si>
-  <si>
-    <t>Assignment-23-  select statement using joins</t>
-  </si>
-  <si>
-    <t>1. Retrieve data from purchase order header table and item table to create purchase order by inner join</t>
-  </si>
-  <si>
-    <t>2. Retrieve data from purchase order header table and item table to create purchase order by for all entries?</t>
-  </si>
-  <si>
-    <t>3. Retrieve data from purchase order header table and item table to create purchase order by parallel curser techAQ1?</t>
-  </si>
-  <si>
-    <t>4. Explore on the exact difference between all of the above techniques?</t>
-  </si>
-  <si>
-    <t>Assignment 22</t>
-  </si>
-  <si>
-    <t>Assignment 23</t>
-  </si>
-  <si>
-    <t>Assignment 20</t>
-  </si>
-  <si>
-    <t>Assignment 21</t>
-  </si>
-  <si>
-    <t>Assignment-24 - debugging</t>
-  </si>
-  <si>
-    <t>1.How many watch points can be created?</t>
-  </si>
-  <si>
-    <t>2.How to add your data from desktop to your internal table in debugging?</t>
-  </si>
-  <si>
-    <t>3.How to check write statements in debugging?</t>
-  </si>
-  <si>
-    <t>5.How to compare variables inside debugging?</t>
-  </si>
-  <si>
-    <t>6.What are the function keys used in debugging?</t>
-  </si>
-  <si>
-    <t>7.Difference between Breakpoints and Watchpoints?</t>
-  </si>
-  <si>
-    <t>Assignment-25 - aggrigate function</t>
-  </si>
-  <si>
-    <t>1.What are aggregate functions and its use?</t>
-  </si>
-  <si>
-    <t>2.what are the types of aggregate functions and explain?</t>
-  </si>
-  <si>
-    <t>3.Create all types of aggregate functions using a custom table?</t>
-  </si>
-  <si>
-    <t>4.which data types are not used in aggregate functions?</t>
-  </si>
-  <si>
-    <t>5.Create a program by adding all aggregate functions in single select statement using any standard data base table?</t>
-  </si>
-  <si>
-    <t>Assignment-26 - inline declaration</t>
-  </si>
-  <si>
-    <t>1. Retrieve data from sales order header (VBAK) &amp; item (VBAP) by for all entries &amp; use inline declaration?</t>
-  </si>
-  <si>
-    <t>2. Check all select statement by inline declaration?</t>
   </si>
   <si>
     <r>
@@ -712,55 +764,20 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>?</t>
     </r>
   </si>
   <si>
-    <t>Assignment-27 - field symbol</t>
-  </si>
-  <si>
-    <t>1.What is Filed symbol ? types of field symbols?</t>
-  </si>
-  <si>
-    <t>2.Difference between Work area and field  Symbol?</t>
-  </si>
-  <si>
-    <t>3.Fetch 100 records from mara and change material type  'FERT'  to  'FT'  and  'SERV '  to  'SE'  and display them in table formate (Dont use work area in program use  typed field symbols).</t>
-  </si>
-  <si>
-    <t>4. Fetch 100 records from sales order header and change sales doc to '0000000001' for seles doc '0000018341'  and  '0000018345' and display them in table formate (Dont use work area in program use  typed field symbols).</t>
-  </si>
-  <si>
-    <t>5.Use Parallel curser with field symbol</t>
-  </si>
-  <si>
-    <t>ZKR_RP_PC_FS</t>
-  </si>
-  <si>
-    <t>Assignment 27</t>
-  </si>
-  <si>
-    <t>4.How we can change internal table data in debugging?(refer assignment 20 5th question)</t>
-  </si>
-  <si>
-    <t>8.How many external breakpoints is possible in session?</t>
-  </si>
-  <si>
-    <t>9. How to deactivate breakpoint in runtime and how to delete breakpoint at runtime?</t>
-  </si>
-  <si>
-    <t>10.What is the use stack?</t>
-  </si>
-  <si>
-    <t>Assignment 24</t>
+    <t>4.How we can change internal table data in debugging?(refer assignment 20 at 5th question)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -868,73 +885,25 @@
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF242424"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <color rgb="FF242424"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="20"/>
       <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF242424"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF00B0F0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -970,7 +939,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -990,7 +959,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1000,29 +968,19 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1030,17 +988,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1360,37 +1321,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E234"/>
+  <dimension ref="A2:E239"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="147.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="35.77734375" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="147.33203125" style="22" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="35.77734375" style="22" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="22"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B2" s="15"/>
-    </row>
-    <row r="3" spans="1:3" s="11" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="B2" s="12"/>
+    </row>
+    <row r="3" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>46049</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1405,17 +1367,17 @@
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
-      <c r="C9" s="16"/>
+      <c r="C9" s="25"/>
     </row>
     <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -1440,11 +1402,11 @@
     <row r="14" spans="1:3" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
     </row>
-    <row r="15" spans="1:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1474,11 +1436,11 @@
     <row r="21" spans="2:3" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1513,11 +1475,11 @@
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B30" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1552,11 +1514,11 @@
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1603,14 +1565,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>46053</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="8" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1645,14 +1607,14 @@
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>46055</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="7" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1707,20 +1669,20 @@
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="1:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>46056</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C69" s="9" t="s">
+      <c r="C69" s="8" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B70" s="1"/>
-      <c r="C70" s="14" t="s">
+      <c r="C70" s="26" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1762,14 +1724,14 @@
     <row r="78" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
     </row>
-    <row r="79" spans="1:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>46057</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="8" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1782,7 +1744,7 @@
       <c r="B81" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="13" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1800,7 +1762,7 @@
       <c r="B84" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="13" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1808,7 +1770,7 @@
       <c r="B85" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="13" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1835,14 +1797,14 @@
     <row r="90" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:4" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>46058</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C91" s="9" t="s">
+      <c r="C91" s="8" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1882,681 +1844,706 @@
       </c>
     </row>
     <row r="99" spans="2:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" spans="2:4" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B100" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="101" spans="2:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="14" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="102" spans="2:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B102" s="18" t="s">
+      <c r="B102" s="14" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="103" spans="2:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="14" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="104" spans="2:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B104" s="18" t="s">
+      <c r="B104" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="105" spans="2:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B105" s="18" t="s">
+      <c r="B105" s="14" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="106" spans="2:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="B106" s="18" t="s">
+      <c r="B106" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D106" s="17" t="s">
+      <c r="D106" s="13" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="107" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B107" s="20" t="s">
+      <c r="B107" s="16" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="109" spans="2:4" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B109" s="19" t="s">
+    <row r="109" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B109" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="7" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="110" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B110" s="20" t="s">
+      <c r="B110" s="16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="111" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B111" s="20" t="s">
+      <c r="B111" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="112" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B112" s="20" t="s">
+      <c r="B112" s="16" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="113" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B113" s="20" t="s">
+      <c r="B113" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="114" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B114" s="20" t="s">
+      <c r="B114" s="16" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="115" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B115" s="20" t="s">
+      <c r="B115" s="16" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="116" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B116" s="20" t="s">
+      <c r="B116" s="16" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="118" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B118" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="7" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="119" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B119" s="18" t="s">
+      <c r="B119" s="14" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="120" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B120" s="18" t="s">
+      <c r="B120" s="14" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="121" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B121" s="18" t="s">
+      <c r="B121" s="14" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="122" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B122" s="18" t="s">
+      <c r="B122" s="14" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="123" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B123" s="18" t="s">
+      <c r="B123" s="14" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="124" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B124" s="18" t="s">
+      <c r="B124" s="14" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="125" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B125" s="18" t="s">
+      <c r="B125" s="14" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="126" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B126" s="18" t="s">
+      <c r="B126" s="14" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="127" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B127" s="18" t="s">
+      <c r="B127" s="14" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="128" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B128" s="18"/>
-    </row>
-    <row r="129" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+      <c r="B128" s="14"/>
+    </row>
+    <row r="129" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B129" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="7" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="130" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B130" s="18" t="s">
+      <c r="B130" s="14" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="131" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B131" s="18" t="s">
+      <c r="B131" s="14" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="132" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B132" s="18" t="s">
+      <c r="B132" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="133" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B133" s="18" t="s">
+      <c r="B133" s="14" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="134" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B134" s="18" t="s">
+      <c r="B134" s="14" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="135" spans="2:3" ht="18" x14ac:dyDescent="0.3">
-      <c r="B135" s="18"/>
-    </row>
-    <row r="136" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B136" s="23" t="s">
+      <c r="B135" s="14"/>
+    </row>
+    <row r="136" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B136" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="7" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="137" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="B137" s="21" t="s">
+    <row r="137" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B137" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="138" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="B138" s="21" t="s">
+    <row r="138" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B138" s="17" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="139" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="B139" s="21" t="s">
+    <row r="139" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B139" s="17" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="140" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="B140" s="21" t="s">
+    <row r="140" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B140" s="17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="141" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="B141" s="21" t="s">
+    <row r="141" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B141" s="17" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="142" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B142" s="22" t="s">
+      <c r="B142" s="19" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="143" spans="2:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
-      <c r="B143" s="21" t="s">
+    <row r="143" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B143" s="17" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="144" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B144" s="22" t="s">
+      <c r="B144" s="19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="146" spans="2:4" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B146" s="19" t="s">
+    <row r="146" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B146" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="7" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="147" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B147" s="24" t="s">
+      <c r="B147" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="D147" s="17" t="s">
+      <c r="D147" s="13" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="148" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B148" s="24" t="s">
+      <c r="B148" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D148" s="17" t="s">
+      <c r="D148" s="13" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="149" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B149" s="24" t="s">
+      <c r="B149" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="D149" s="17" t="s">
+      <c r="D149" s="13" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="150" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B150" s="24" t="s">
+      <c r="B150" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D150" s="17" t="s">
+      <c r="D150" s="13" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="151" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B151" s="24" t="s">
+      <c r="B151" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="D151" s="17" t="s">
+      <c r="D151" s="13" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="152" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B152" s="24" t="s">
+      <c r="B152" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D152" s="17" t="s">
+      <c r="D152" s="13" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="153" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B153" s="24" t="s">
+      <c r="B153" s="17" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="155" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B155" s="20" t="s">
+      <c r="B155" s="16" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="156" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B156" s="20" t="s">
+      <c r="B156" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="158" spans="2:4" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B158" s="27" t="s">
+    <row r="158" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B158" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="C158" s="8" t="s">
+      <c r="C158" s="7" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="159" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B159" s="25" t="s">
+      <c r="B159" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="D159" s="17" t="s">
+      <c r="D159" s="13" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="160" spans="2:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="B160" s="25" t="s">
+      <c r="B160" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D160" s="17" t="s">
+      <c r="D160" s="13" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="161" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B161" s="25" t="s">
+      <c r="B161" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="D161" s="17" t="s">
+      <c r="D161" s="13" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="162" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B162" s="25" t="s">
+      <c r="B162" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="D162" s="17" t="s">
+      <c r="D162" s="13" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="163" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B163" s="26" t="s">
+      <c r="B163" s="19" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="164" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B164" s="24" t="s">
+      <c r="B164" s="17" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="166" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B166" s="20" t="s">
+      <c r="B166" s="16" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="167" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B167" s="28" t="s">
+      <c r="B167" s="21" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="168" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B168" s="20" t="s">
+      <c r="B168" s="16" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="170" spans="2:5" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B170" s="29" t="s">
+    <row r="170" spans="2:5" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B170" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C170" s="8" t="s">
+      <c r="C170" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="171" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B171" s="26" t="s">
+      <c r="B171" s="19" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="172" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B172" s="26" t="s">
+      <c r="B172" s="19" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="173" spans="2:5" ht="18" x14ac:dyDescent="0.35">
-      <c r="B173" s="26" t="s">
+      <c r="B173" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C173" s="26"/>
-      <c r="D173" s="26"/>
-      <c r="E173" s="26"/>
-    </row>
-    <row r="175" spans="2:5" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B175" s="23" t="s">
+      <c r="C173" s="19"/>
+      <c r="D173" s="19"/>
+      <c r="E173" s="19"/>
+    </row>
+    <row r="175" spans="2:5" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B175" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C175" s="8" t="s">
+      <c r="C175" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5" ht="18" x14ac:dyDescent="0.35">
+      <c r="B176" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B177" s="19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B178" s="19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B179" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B180" s="19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="182" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B182" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="C182" s="7" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="176" spans="2:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B176" s="30" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="177" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B177" s="30" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="178" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B178" s="30" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="179" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B179" s="30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="180" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B180" s="30" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="182" spans="2:3" s="7" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B182" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="C182" s="8" t="s">
+    <row r="183" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B183" s="18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="184" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B184" s="18" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="185" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B185" s="18" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="186" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B186" s="18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="187" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B187" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="189" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B189" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="190" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B190" s="19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="191" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B191" s="27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="192" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B192" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="193" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B193" s="19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="194" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B194" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="195" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B195" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="197" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B197" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="198" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B198" s="28" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B199" s="28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="200" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B200" s="28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="201" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B201" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="204" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B204" s="15" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="183" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B183" s="31" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="184" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B184" s="31" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="185" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B185" s="31" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="186" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B186" s="31" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="187" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B187" s="31" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="189" spans="2:3" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B189" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="C189" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="190" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B190" s="30" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="191" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B191" s="32" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="192" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B192" s="33" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="193" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B193" s="30" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="194" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B194" s="30" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="195" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B195" s="30" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="197" spans="2:3" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B197" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="C197" s="8" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="198" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B198" s="35" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="199" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B199" s="35" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="200" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B200" s="35" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="201" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B201" s="30" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="204" spans="2:3" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B204" s="34" t="s">
+      <c r="C204" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B205" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="C204" s="8" t="s">
+    </row>
+    <row r="206" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B206" s="19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="207" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B207" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="208" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B208" s="19" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B209" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B210" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B211" s="19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B212" s="19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B213" s="19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B214" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B216" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B217" s="19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B218" s="19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B219" s="19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B220" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B221" s="19" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B222" s="19"/>
+    </row>
+    <row r="223" spans="2:2" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B223" s="15" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B224" s="17" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B225" s="17" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B226" s="17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B227" s="17"/>
+    </row>
+    <row r="228" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="B228" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="229" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B229" s="19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="230" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B230" s="19" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="231" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B231" s="19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="232" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B232" s="19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="233" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B233" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="D233" s="13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="234" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B234" s="19"/>
+    </row>
+    <row r="235" spans="2:4" s="24" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B235" s="29" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="236" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B236" s="19" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="237" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B237" s="19" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="205" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B205" s="30" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="206" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B206" s="30" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="207" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B207" s="30" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="208" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B208" s="30" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="209" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B209" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="210" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B210" s="30" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="211" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B211" s="30" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="212" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B212" s="30" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="213" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B213" s="30" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="214" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B214" s="30" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="216" spans="2:2" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B216" s="34" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="217" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B217" s="30" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="218" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B218" s="30" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="219" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B219" s="30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="220" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B220" s="30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="221" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B221" s="30" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="222" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B222" s="30"/>
-    </row>
-    <row r="223" spans="2:2" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B223" s="34" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="224" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B224" s="33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="225" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B225" s="33" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="226" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B226" s="33" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="227" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B227" s="33"/>
-    </row>
-    <row r="228" spans="2:4" s="7" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B228" s="34" t="s">
-        <v>219</v>
-      </c>
-      <c r="C228" s="8" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="229" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B229" s="30" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="230" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B230" s="30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="231" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B231" s="30" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="232" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B232" s="30" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="233" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B233" s="30" t="s">
-        <v>224</v>
-      </c>
-      <c r="D233" s="17" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="234" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B234" s="30"/>
+    <row r="238" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B238" s="19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="239" spans="2:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B239" s="19" t="s">
+        <v>233</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="510" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C673EB-ACFE-4CB4-93DA-35F80C8CD221}"/>
+  <xr:revisionPtr revIDLastSave="527" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B48196B1-2CD8-495E-80CE-DB5F060D1098}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="240">
   <si>
     <t>Date</t>
   </si>
@@ -771,6 +771,15 @@
   </si>
   <si>
     <t>4.How we can change internal table data in debugging?(refer assignment 20 at 5th question)</t>
+  </si>
+  <si>
+    <t>ASSIGNMENT-29 - Selection screen</t>
+  </si>
+  <si>
+    <t>1.Create the DDIC 7 Object Page?</t>
+  </si>
+  <si>
+    <t>Selection Screen.</t>
   </si>
 </sst>
 </file>
@@ -939,7 +948,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -988,13 +997,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1018,10 +1026,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1321,20 +1325,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E239"/>
+  <dimension ref="A2:E244"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" style="22" customWidth="1"/>
-    <col min="2" max="2" width="147.33203125" style="22" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" style="22" customWidth="1"/>
-    <col min="4" max="4" width="35.77734375" style="22" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="22"/>
+    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="2" max="2" width="147.33203125" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="35.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="12"/>
     </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" s="22" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
@@ -1345,7 +1348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>46049</v>
       </c>
@@ -1367,7 +1370,7 @@
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
@@ -1377,7 +1380,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="1"/>
-      <c r="C9" s="25"/>
+      <c r="C9" s="24"/>
     </row>
     <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
@@ -1402,7 +1405,7 @@
     <row r="14" spans="1:3" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
     </row>
-    <row r="15" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B15" s="6" t="s">
         <v>12</v>
       </c>
@@ -1436,7 +1439,7 @@
     <row r="21" spans="2:3" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B22" s="6" t="s">
         <v>17</v>
       </c>
@@ -1475,7 +1478,7 @@
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B30" s="6" t="s">
         <v>23</v>
       </c>
@@ -1514,7 +1517,7 @@
     <row r="37" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B37" s="1"/>
     </row>
-    <row r="38" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>46053</v>
       </c>
@@ -1607,7 +1610,7 @@
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>46055</v>
       </c>
@@ -1669,7 +1672,7 @@
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B68" s="1"/>
     </row>
-    <row r="69" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>46056</v>
       </c>
@@ -1682,7 +1685,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B70" s="1"/>
-      <c r="C70" s="26" t="s">
+      <c r="C70" s="25" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1724,7 +1727,7 @@
     <row r="78" spans="1:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B78" s="2"/>
     </row>
-    <row r="79" spans="1:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>46057</v>
       </c>
@@ -1797,7 +1800,7 @@
     <row r="90" spans="1:4" ht="18" x14ac:dyDescent="0.3">
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>46058</v>
       </c>
@@ -1844,7 +1847,7 @@
       </c>
     </row>
     <row r="99" spans="2:4" ht="16.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="100" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:4" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B100" s="6" t="s">
         <v>88</v>
       </c>
@@ -1890,7 +1893,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="109" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:4" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B109" s="15" t="s">
         <v>102</v>
       </c>
@@ -1933,7 +1936,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="118" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B118" s="6" t="s">
         <v>110</v>
       </c>
@@ -1989,7 +1992,7 @@
     <row r="128" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B128" s="14"/>
     </row>
-    <row r="129" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.35">
       <c r="B129" s="6" t="s">
         <v>121</v>
       </c>
@@ -2025,7 +2028,7 @@
     <row r="135" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B135" s="14"/>
     </row>
-    <row r="136" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B136" s="15" t="s">
         <v>127</v>
       </c>
@@ -2073,7 +2076,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="146" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:4" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B146" s="15" t="s">
         <v>136</v>
       </c>
@@ -2144,7 +2147,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="158" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:4" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B158" s="20" t="s">
         <v>153</v>
       </c>
@@ -2209,7 +2212,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="170" spans="2:5" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:5" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B170" s="15" t="s">
         <v>168</v>
       </c>
@@ -2235,7 +2238,7 @@
       <c r="D173" s="19"/>
       <c r="E173" s="19"/>
     </row>
-    <row r="175" spans="2:5" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:5" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B175" s="15" t="s">
         <v>174</v>
       </c>
@@ -2268,7 +2271,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B182" s="15" t="s">
         <v>180</v>
       </c>
@@ -2301,7 +2304,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="189" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B189" s="15" t="s">
         <v>186</v>
       </c>
@@ -2315,7 +2318,7 @@
       </c>
     </row>
     <row r="191" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B191" s="27" t="s">
+      <c r="B191" s="26" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2339,7 +2342,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="197" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B197" s="15" t="s">
         <v>192</v>
       </c>
@@ -2348,17 +2351,17 @@
       </c>
     </row>
     <row r="198" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B198" s="28" t="s">
+      <c r="B198" s="27" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="199" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B199" s="28" t="s">
+      <c r="B199" s="27" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="200" spans="2:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="B200" s="28" t="s">
+      <c r="B200" s="27" t="s">
         <v>195</v>
       </c>
     </row>
@@ -2367,7 +2370,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="204" spans="2:3" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B204" s="15" t="s">
         <v>201</v>
       </c>
@@ -2425,7 +2428,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="216" spans="2:2" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:2" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B216" s="15" t="s">
         <v>208</v>
       </c>
@@ -2458,7 +2461,7 @@
     <row r="222" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B222" s="19"/>
     </row>
-    <row r="223" spans="2:2" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:2" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B223" s="15" t="s">
         <v>214</v>
       </c>
@@ -2481,7 +2484,7 @@
     <row r="227" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B227" s="17"/>
     </row>
-    <row r="228" spans="2:4" s="24" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:4" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.45">
       <c r="B228" s="15" t="s">
         <v>217</v>
       </c>
@@ -2520,8 +2523,8 @@
     <row r="234" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B234" s="19"/>
     </row>
-    <row r="235" spans="2:4" s="24" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="B235" s="29" t="s">
+    <row r="235" spans="2:4" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B235" s="28" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2543,6 +2546,21 @@
     <row r="239" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B239" s="19" t="s">
         <v>233</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B242" s="28" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B243" s="19" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="244" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B244" s="19" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>

--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f10c37138a14469/Desktop/SAP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5F10C37138A14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="527" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B48196B1-2CD8-495E-80CE-DB5F060D1098}"/>
+  <xr:revisionPtr revIDLastSave="572" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85BBA1FA-A523-4D92-A886-39B1AB5F7AAF}"/>
   <bookViews>
-    <workbookView xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="1428" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="322">
   <si>
     <t>Date</t>
   </si>
@@ -781,12 +781,344 @@
   <si>
     <t>Selection Screen.</t>
   </si>
+  <si>
+    <t>Assignment-30- classical report</t>
+  </si>
+  <si>
+    <t>1.what are the events in Classical report?</t>
+  </si>
+  <si>
+    <t>2.Difference between Initialization and at selection screen event?</t>
+  </si>
+  <si>
+    <t>3.What is the use of start-of-selection event &amp; can we create program without start-of-selection?</t>
+  </si>
+  <si>
+    <t>4.which event will trigger first at selection screen and at selection output?</t>
+  </si>
+  <si>
+    <t>5.Difference between At selection screen and At selection screen output?</t>
+  </si>
+  <si>
+    <t>6.Create a report which consist all classical reports events and debug it 25 times?</t>
+  </si>
+  <si>
+    <t>7.What is the triggering sequence of classical report events?</t>
+  </si>
+  <si>
+    <t>Assignment 30</t>
+  </si>
+  <si>
+    <t>Assignment 28</t>
+  </si>
+  <si>
+    <t>Assignment 29</t>
+  </si>
+  <si>
+    <t>Assignment-31 - interactive report ( hide )</t>
+  </si>
+  <si>
+    <t>1.What is Interactive report?</t>
+  </si>
+  <si>
+    <t>2.what is the use of interactive reporting?</t>
+  </si>
+  <si>
+    <t>3.What are the events we use in interactive report and explain that?</t>
+  </si>
+  <si>
+    <r>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Create interactive report using VBRK and VBRP tables (using new syntax) with hide technique up to 10 rows?</t>
+    </r>
+  </si>
+  <si>
+    <t>Assignment 31</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>what is get cursor field technique and its use?</t>
+    </r>
+  </si>
+  <si>
+    <t>2.List down the system variables available in interactive report and its uses(you need to show practically )?</t>
+  </si>
+  <si>
+    <t>3.How many lists are available for the system variables?</t>
+  </si>
+  <si>
+    <t>4.What system fields do we use for interactive reporting?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.Create the interactive report by using get cursor technique and use top of page and end of page events, for example it is a basic list it shows the VBRK (Master Data) </t>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>table and if it is a secondary list it is showing a VBRP (Item data). In each page show only 15records see the example in below picture show the output by using colors and borders</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>and it is in a tabular format. maintain the top-of-page during line selection and end-of-page during line selection. in end of page display user name, time, date.</t>
+    </r>
+  </si>
+  <si>
+    <t>Note: VBRK-&gt; HEADER, VBRP-&gt;ITEM. Use New syntax don't create unwanted structures.</t>
+  </si>
+  <si>
+    <t>Assignment-33 - modularization(includes)</t>
+  </si>
+  <si>
+    <t>1.What is variant? How to create variant, Explain it?</t>
+  </si>
+  <si>
+    <t>2.What is Modularization techniques and Types of it?</t>
+  </si>
+  <si>
+    <t>3.What is syntax of include and create one include and use it in program?</t>
+  </si>
+  <si>
+    <t>4.Can we use includes in FM?</t>
+  </si>
+  <si>
+    <t>5.What is subroutine and use of it?</t>
+  </si>
+  <si>
+    <t>6.What are the key word used in subroutine?</t>
+  </si>
+  <si>
+    <t>7.Create one subroutine example in program using vbap to fetch the data?</t>
+  </si>
+  <si>
+    <t>8.After Endform can we access write statement. if yes how if no why?</t>
+  </si>
+  <si>
+    <t>Assignment-34 - modularization (subroutines)</t>
+  </si>
+  <si>
+    <t>1. Explore and go through each radio button while creating Tcode and how to create T-code?</t>
+  </si>
+  <si>
+    <t>2. Can we create variant for Tcode ? if yes then how?</t>
+  </si>
+  <si>
+    <t>3. Difference between pass by value and pass by reference?</t>
+  </si>
+  <si>
+    <t>4. Difference between actual parameters and formal parameters?</t>
+  </si>
+  <si>
+    <t>5. Create a subroutine by key words like using and changing?</t>
+  </si>
+  <si>
+    <t>6. Practice on actual, formal and pass by value, pass by reference in program?</t>
+  </si>
+  <si>
+    <t>7. How to create subroutine pool practically?</t>
+  </si>
+  <si>
+    <t>8. Create external subroutine?</t>
+  </si>
+  <si>
+    <t>Assignment-35 - modularization (function module)</t>
+  </si>
+  <si>
+    <t>1)What is function module and function group?</t>
+  </si>
+  <si>
+    <t>2)Types of function module?</t>
+  </si>
+  <si>
+    <t>3)Explore all the tabs present in function module?</t>
+  </si>
+  <si>
+    <t>4)Create a function module and fetch the records using se38.</t>
+  </si>
+  <si>
+    <t>--&gt; using vbap or vbak.</t>
+  </si>
+  <si>
+    <t>5) Go through Rfc function module</t>
+  </si>
+  <si>
+    <t>6).what is pass by value and pass by reference</t>
+  </si>
+  <si>
+    <t>7. How many FM are possible to create one Function Group</t>
+  </si>
+  <si>
+    <t>8. Difference between FM and subroutine</t>
+  </si>
+  <si>
+    <t>9. Create Exception and call ur program based on condition</t>
+  </si>
+  <si>
+    <t>Assignment-36 - modularization ( rfc function module)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> . </t>
+  </si>
+  <si>
+    <t>2) What are the parameters are allowed while creating rfc function module?</t>
+  </si>
+  <si>
+    <t>3) Create one structure in se11 with 3 to 4 field from table EKPO, after that you will develop a RFC function module in hana server and calling system will be ECC.</t>
+  </si>
+  <si>
+    <t>4) types of rfc , explain it?</t>
+  </si>
+  <si>
+    <t>5) what is luw  and use of luw?</t>
+  </si>
+  <si>
+    <t>6) Difference between Database luw and SAP luw?</t>
+  </si>
+  <si>
+    <t>7) what is update FM ? why we go for update function module?</t>
+  </si>
+  <si>
+    <t>8) which parameters support in update fm? and why?</t>
+  </si>
+  <si>
+    <t>9) what are V1 and V2 types of update function module?</t>
+  </si>
+  <si>
+    <t>10) Create update function module with CRUD(create ,read,update and delete) operations?</t>
+  </si>
+  <si>
+    <t>11)what is commit work and commit work and wait.</t>
+  </si>
+  <si>
+    <t>12)how to debug update FM?</t>
+  </si>
+  <si>
+    <t>13)Diffrence between commit work and roll back?</t>
+  </si>
+  <si>
+    <t>14)Diffrence between Normal,rfc and update function module?</t>
+  </si>
+  <si>
+    <t>Assignment-37 - modularization (update function module)</t>
+  </si>
+  <si>
+    <t>1. Create ztable (take 6 fields) perform the crud operations(insert, update, delete and read). All the open sql statements will be inside the Update</t>
+  </si>
+  <si>
+    <t>Function module only.</t>
+  </si>
+  <si>
+    <t>Note :</t>
+  </si>
+  <si>
+    <t>--&gt; key field is the combination of caracters and numbers use and id is auto generated ex : (ID00001, ID00002,......).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ( ex: use snro tcode or else connect with ur mentors)</t>
+  </si>
+  <si>
+    <t>--&gt; All the validations and business logic should be inside the function module.</t>
+  </si>
+  <si>
+    <t>--&gt; Make use of subroutines if possible.</t>
+  </si>
+  <si>
+    <t>Note :Use message class Validation is compulsory for all the fields.</t>
+  </si>
+  <si>
+    <t>Assignment 33</t>
+  </si>
+  <si>
+    <t>Assignment 34</t>
+  </si>
+  <si>
+    <t>Assignment 36</t>
+  </si>
+  <si>
+    <t>Assignment-32 - get curser technique in interactive report</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -914,6 +1246,76 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF202124"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Symbol"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -948,7 +1350,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1010,6 +1412,32 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1325,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E244"/>
+  <dimension ref="A2:E327"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -2527,6 +2955,9 @@
       <c r="B235" s="28" t="s">
         <v>229</v>
       </c>
+      <c r="C235" s="32" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="236" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B236" s="19" t="s">
@@ -2548,19 +2979,427 @@
         <v>233</v>
       </c>
     </row>
-    <row r="242" spans="2:2" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="242" spans="2:3" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B242" s="28" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="243" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="C242" s="32" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="243" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B243" s="19" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="244" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+    <row r="244" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B244" s="19" t="s">
         <v>239</v>
+      </c>
+    </row>
+    <row r="246" spans="2:3" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B246" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="C246" s="32" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B247" s="29" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="248" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B248" s="29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="249" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B249" s="29" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="250" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B250" s="30" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="251" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B251" s="29" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="252" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B252" s="29" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="253" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B253" s="29" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="255" spans="2:3" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B255" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="C255" s="32" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="256" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B256" s="33" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="257" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B257" s="30" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="258" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B258" s="29" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="259" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B259" s="29" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B261" s="31" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="262" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B262" s="30" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="263" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B263" s="29" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="264" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B264" s="29" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="265" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B265" s="29" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="266" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B266" s="29" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="267" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B267" s="34" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="268" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B268" s="34" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="269" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B269" s="29" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="270" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B270" s="35"/>
+    </row>
+    <row r="271" spans="2:3" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B271" s="31" t="s">
+        <v>265</v>
+      </c>
+      <c r="C271" s="32" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="272" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B272" s="29" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="273" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B273" s="29" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="274" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B274" s="29" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="275" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B275" s="29" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="276" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B276" s="29" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="277" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B277" s="29" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="278" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B278" s="29" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="279" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B279" s="29" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="280" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B280" s="29"/>
+    </row>
+    <row r="281" spans="2:3" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B281" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="C281" s="32" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="282" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B282" s="29" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="283" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B283" s="29" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="284" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B284" s="29" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="285" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B285" s="29" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="286" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B286" s="29" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="287" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B287" s="29" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="288" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B288" s="29" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="289" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B289" s="29" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="290" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B290" s="35"/>
+    </row>
+    <row r="291" spans="2:3" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B291" s="28" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="292" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B292" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="293" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B293" s="14" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="294" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B294" s="14" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="295" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B295" s="14" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="296" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B296" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="297" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B297" s="36" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="298" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B298" s="37" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="299" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B299" s="37" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B300" s="37" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B301" s="37" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="302" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B302" s="35"/>
+    </row>
+    <row r="303" spans="2:3" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="B303" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="C303" s="32" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B304" s="19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="305" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B305" s="14" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="306" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B306" s="14" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="307" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B307" s="14" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="308" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B308" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="309" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B309" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="310" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B310" s="14" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="311" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B311" s="14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="312" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B312" s="14" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="313" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B313" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="314" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B314" s="14" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="315" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B315" s="14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="316" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B316" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="317" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B317" s="14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="318" spans="2:2" ht="21" x14ac:dyDescent="0.3">
+      <c r="B318" s="38"/>
+    </row>
+    <row r="319" spans="2:2" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="B319" s="40" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="320" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B320" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="321" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B321" s="14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="322" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B322" s="14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="323" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B323" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="324" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B324" s="14" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="325" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B325" s="14" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="326" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B326" s="14" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="327" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B327" s="14" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -2591,8 +3430,15 @@
     <hyperlink ref="C182" r:id="rId24" xr:uid="{F4F4C03C-5982-4E12-A7D9-612B9828C231}"/>
     <hyperlink ref="C228" r:id="rId25" xr:uid="{2277D97B-A360-4242-8244-55BB1729762C}"/>
     <hyperlink ref="C204" r:id="rId26" xr:uid="{1AEE8A7C-CF6E-49EC-AFFD-4E0A8D389E0B}"/>
+    <hyperlink ref="C246" r:id="rId27" xr:uid="{7D6F7250-6815-431D-AA3B-9B22048CAB23}"/>
+    <hyperlink ref="C235" r:id="rId28" xr:uid="{DD6AF810-7CA8-4B20-9F3A-E3FDAC18AECD}"/>
+    <hyperlink ref="C242" r:id="rId29" xr:uid="{62202167-ED7A-49BA-B8D6-85E0C5FCBACB}"/>
+    <hyperlink ref="C255" r:id="rId30" xr:uid="{81EA8113-D43E-4F9F-BDF0-A1429892F887}"/>
+    <hyperlink ref="C271" r:id="rId31" xr:uid="{F3825B61-C252-47C4-B4B9-F1DF030EF5F0}"/>
+    <hyperlink ref="C281" r:id="rId32" xr:uid="{27F317B1-B4E8-48AD-8DA0-3AB258A76594}"/>
+    <hyperlink ref="C303" r:id="rId33" xr:uid="{FE0D6467-E78B-4599-9202-BF40FD2B2BDD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId27"/>
+  <pageSetup orientation="portrait" r:id="rId34"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5F10C37138A14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="572" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{85BBA1FA-A523-4D92-A886-39B1AB5F7AAF}"/>
+  <xr:revisionPtr revIDLastSave="623" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{774270BE-A16B-4F67-8476-9971679C68DD}"/>
   <bookViews>
-    <workbookView xWindow="1428" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="1776" yWindow="2196" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="340">
   <si>
     <t>Date</t>
   </si>
@@ -1113,12 +1113,66 @@
   <si>
     <t>Assignment-32 - get curser technique in interactive report</t>
   </si>
+  <si>
+    <t>ALV:</t>
+  </si>
+  <si>
+    <t>1. What is ALV? Types of ALV.</t>
+  </si>
+  <si>
+    <t>2. Function module we used</t>
+  </si>
+  <si>
+    <t>3. Difference between list display and grid display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. What is field catalogue </t>
+  </si>
+  <si>
+    <t>5. What are the fields present in field catalogue</t>
+  </si>
+  <si>
+    <t>6.what are the types of function module used in alv to display the output format?</t>
+  </si>
+  <si>
+    <t>7.Create alv report to display the purchase order details in list format?</t>
+  </si>
+  <si>
+    <t>8.Create alv report to display the sales order details in grid format?</t>
+  </si>
+  <si>
+    <t>9.Create alv report to fetch the data(using some particular fields) by using mara and marc in grid format?</t>
+  </si>
+  <si>
+    <t>10,Explain the difference between classical,interactive and alv?</t>
+  </si>
+  <si>
+    <t>11.Explain the diffrence between List and Grid display?</t>
+  </si>
+  <si>
+    <t>Assignment-38 -ALV Report</t>
+  </si>
+  <si>
+    <t>1)Create alv report using field catlog of material table?</t>
+  </si>
+  <si>
+    <t>no hrizontal and hotspot.</t>
+  </si>
+  <si>
+    <t>Assignment 38</t>
+  </si>
+  <si>
+    <t>2)Create an alv report for billing document details to display data in grid format and using layout how to achive column optimaization,edit,no virtical,</t>
+  </si>
+  <si>
+    <t>3)Create an alv report for spfli table for total and subtotal?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1316,8 +1370,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF002060"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1336,6 +1398,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1350,7 +1418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1436,6 +1504,10 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1753,7 +1825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E327"/>
+  <dimension ref="A2:E346"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -3367,39 +3439,130 @@
         <v>310</v>
       </c>
     </row>
-    <row r="321" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="321" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B321" s="14" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="322" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B322" s="14" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="323" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="323" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B323" s="14" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="324" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="324" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B324" s="14" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="325" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B325" s="14" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="326" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="326" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B326" s="14" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="327" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="327" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B327" s="14" t="s">
         <v>317</v>
+      </c>
+    </row>
+    <row r="328" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B328" s="14"/>
+    </row>
+    <row r="329" spans="2:3" s="41" customFormat="1" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="B329" s="42" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="330" spans="2:3" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="B330" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C330" s="32" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="331" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B331" s="14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="332" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B332" s="14" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="333" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B333" s="14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="334" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B334" s="14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="335" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B335" s="14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="336" spans="2:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B336" s="14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="337" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B337" s="14" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="338" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B338" s="14" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="339" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B339" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="340" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B340" s="14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="341" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B341" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="343" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B343" s="14" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="344" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B344" s="14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="345" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B345" s="14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="346" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+      <c r="B346" s="14" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -3437,8 +3600,9 @@
     <hyperlink ref="C271" r:id="rId31" xr:uid="{F3825B61-C252-47C4-B4B9-F1DF030EF5F0}"/>
     <hyperlink ref="C281" r:id="rId32" xr:uid="{27F317B1-B4E8-48AD-8DA0-3AB258A76594}"/>
     <hyperlink ref="C303" r:id="rId33" xr:uid="{FE0D6467-E78B-4599-9202-BF40FD2B2BDD}"/>
+    <hyperlink ref="C330" r:id="rId34" xr:uid="{8D01ECEB-758E-4418-9BC5-2A7896C3F34C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId34"/>
+  <pageSetup orientation="portrait" r:id="rId35"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5F10C37138A14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="623" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{774270BE-A16B-4F67-8476-9971679C68DD}"/>
+  <xr:revisionPtr revIDLastSave="680" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC150C7D-E1DF-44A7-8C99-B35A9F50DC3C}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="2196" windowWidth="17280" windowHeight="8880" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="377">
   <si>
     <t>Date</t>
   </si>
@@ -1167,12 +1167,123 @@
   <si>
     <t>3)Create an alv report for spfli table for total and subtotal?</t>
   </si>
+  <si>
+    <t>2.What is SAP Memory and Abap Memory differences</t>
+  </si>
+  <si>
+    <t>1.What is memory management?</t>
+  </si>
+  <si>
+    <t>3.How to declare parameters in another session?</t>
+  </si>
+  <si>
+    <t>Assignment 39-SAP Memory and ABAP Memory</t>
+  </si>
+  <si>
+    <t>Assignment 39</t>
+  </si>
+  <si>
+    <t>Performance tuning:</t>
+  </si>
+  <si>
+    <t>ST05</t>
+  </si>
+  <si>
+    <t>SE30/SAT</t>
+  </si>
+  <si>
+    <t>EPC (Extended Program Check)</t>
+  </si>
+  <si>
+    <t>GUI Upoad and Download</t>
+  </si>
+  <si>
+    <t>Assignment 40-BDC(Batch Data Communication)</t>
+  </si>
+  <si>
+    <t>1.What is BDC in SAP ABAP?</t>
+  </si>
+  <si>
+    <t>2.What are the different methods of BDC?</t>
+  </si>
+  <si>
+    <t>3.What is the difference between Session Method and Call Transaction Method?</t>
+  </si>
+  <si>
+    <t>4.What are the advantages of BDC?</t>
+  </si>
+  <si>
+    <t>5.What are the limitations of BDC?</t>
+  </si>
+  <si>
+    <t>6.What are the main components of a BDC program?</t>
+  </si>
+  <si>
+    <t>7.What is the purpose of the BDCDATA internal table?</t>
+  </si>
+  <si>
+    <t>8.What is the structure of the BDCDATA table?</t>
+  </si>
+  <si>
+    <t>9.What are PROGRAM, DYNPRO, DYNBEGIN, FNAM, and FVAL in BDCDATA?</t>
+  </si>
+  <si>
+    <t>10.What is the role of SHDB (Transaction Recorder) in BDC?</t>
+  </si>
+  <si>
+    <t>1.What is the Call Transaction Method in SAP ABAP?</t>
+  </si>
+  <si>
+    <t>2.What is the syntax of the CALL TRANSACTION statement?</t>
+  </si>
+  <si>
+    <t>3/What are the processing modes available in Call Transaction?</t>
+  </si>
+  <si>
+    <t>A – Display all screens</t>
+  </si>
+  <si>
+    <t>E – Display only error screens</t>
+  </si>
+  <si>
+    <t>N – Background processing (no screens)</t>
+  </si>
+  <si>
+    <t>What is the purpose of the UPDATE option?</t>
+  </si>
+  <si>
+    <t>S – Synchronous update</t>
+  </si>
+  <si>
+    <t>A – Asynchronous update</t>
+  </si>
+  <si>
+    <t>L – Local update</t>
+  </si>
+  <si>
+    <t>4.What is the MESSAGES INTO clause used for?</t>
+  </si>
+  <si>
+    <t>5.Which structure stores the messages generated during Call Transaction?</t>
+  </si>
+  <si>
+    <t>6.What is BDCMSGCOLL?</t>
+  </si>
+  <si>
+    <t>7.How do you display BDC error messages?</t>
+  </si>
+  <si>
+    <t>[7/28,] Basic BDC Questions</t>
+  </si>
+  <si>
+    <t>[7/28] Call Transaction Method Questions</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1378,6 +1489,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1418,7 +1546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1510,6 +1638,8 @@
     <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1825,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E346"/>
+  <dimension ref="A2:E390"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -1892,8 +2022,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="21" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3520,49 +3650,239 @@
         <v>328</v>
       </c>
     </row>
-    <row r="337" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="337" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B337" s="14" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="338" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="338" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B338" s="14" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="339" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="339" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B339" s="14" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="340" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="340" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B340" s="14" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="341" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="341" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B341" s="14" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="343" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="343" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B343" s="14" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="344" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="344" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B344" s="14" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="345" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="345" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B345" s="14" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="346" spans="2:2" ht="18" x14ac:dyDescent="0.3">
+    <row r="346" spans="2:3" ht="18" x14ac:dyDescent="0.3">
       <c r="B346" s="14" t="s">
         <v>339</v>
+      </c>
+    </row>
+    <row r="349" spans="2:3" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="B349" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="C349" s="32" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="350" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B350" s="16" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="351" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B351" s="16" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="352" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B352" s="16" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="354" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B354" s="43" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="355" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B355" s="16" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="356" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B356" s="16" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="357" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B357" s="16" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="359" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B359" s="43" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="362" spans="2:3" s="23" customFormat="1" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="B362" s="40" t="s">
+        <v>350</v>
+      </c>
+      <c r="C362" s="32"/>
+    </row>
+    <row r="363" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B363" s="16"/>
+    </row>
+    <row r="364" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B364" s="44" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="365" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B365" s="16" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="366" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B366" s="16" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="367" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B367" s="16" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="368" spans="2:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="B368" s="16" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="369" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B369" s="16" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="370" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B370" s="16" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="371" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B371" s="16" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="372" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B372" s="16" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="373" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B373" s="16" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="374" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B374" s="16" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="375" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B375" s="16"/>
+    </row>
+    <row r="376" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B376" s="44" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="377" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B377" s="16" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="378" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B378" s="16" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="379" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B379" s="16" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="380" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B380" s="16" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="381" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B381" s="16" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="382" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B382" s="16" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="383" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B383" s="16" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="384" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B384" s="16" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="385" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B385" s="16" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="386" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B386" s="16" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="387" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B387" s="16" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="388" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B388" s="16" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="389" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B389" s="16" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="390" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B390" s="16" t="s">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -3601,8 +3921,9 @@
     <hyperlink ref="C281" r:id="rId32" xr:uid="{27F317B1-B4E8-48AD-8DA0-3AB258A76594}"/>
     <hyperlink ref="C303" r:id="rId33" xr:uid="{FE0D6467-E78B-4599-9202-BF40FD2B2BDD}"/>
     <hyperlink ref="C330" r:id="rId34" xr:uid="{8D01ECEB-758E-4418-9BC5-2A7896C3F34C}"/>
+    <hyperlink ref="C349" r:id="rId35" xr:uid="{A1CEA8FE-2DF9-4EF3-8CC1-9B31F009191E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId35"/>
+  <pageSetup orientation="portrait" r:id="rId36"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5F10C37138A14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC150C7D-E1DF-44A7-8C99-B35A9F50DC3C}"/>
+  <xr:revisionPtr revIDLastSave="688" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44740330-921F-489F-9DA2-325C4D79A2D2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="2976" yWindow="1488" windowWidth="17280" windowHeight="9420" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="378">
   <si>
     <t>Date</t>
   </si>
@@ -1249,9 +1249,6 @@
     <t>N – Background processing (no screens)</t>
   </si>
   <si>
-    <t>What is the purpose of the UPDATE option?</t>
-  </si>
-  <si>
     <t>S – Synchronous update</t>
   </si>
   <si>
@@ -1261,22 +1258,28 @@
     <t>L – Local update</t>
   </si>
   <si>
-    <t>4.What is the MESSAGES INTO clause used for?</t>
-  </si>
-  <si>
-    <t>5.Which structure stores the messages generated during Call Transaction?</t>
-  </si>
-  <si>
-    <t>6.What is BDCMSGCOLL?</t>
-  </si>
-  <si>
-    <t>7.How do you display BDC error messages?</t>
-  </si>
-  <si>
     <t>[7/28,] Basic BDC Questions</t>
   </si>
   <si>
     <t>[7/28] Call Transaction Method Questions</t>
+  </si>
+  <si>
+    <t>4.What is the purpose of the UPDATE option?</t>
+  </si>
+  <si>
+    <t>5.What is the MESSAGES INTO clause used for?</t>
+  </si>
+  <si>
+    <t>6.Which structure stores the messages generated during Call Transaction?</t>
+  </si>
+  <si>
+    <t>7.What is BDCMSGCOLL?</t>
+  </si>
+  <si>
+    <t>8.How do you display BDC error messages?</t>
+  </si>
+  <si>
+    <t>Assignment 40</t>
   </si>
 </sst>
 </file>
@@ -3747,14 +3750,16 @@
       <c r="B362" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="C362" s="32"/>
+      <c r="C362" s="32" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="363" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B363" s="16"/>
     </row>
     <row r="364" spans="2:3" ht="18" x14ac:dyDescent="0.35">
       <c r="B364" s="44" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="365" spans="2:3" ht="18" x14ac:dyDescent="0.35">
@@ -3812,7 +3817,7 @@
     </row>
     <row r="376" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B376" s="44" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="377" spans="2:2" ht="18" x14ac:dyDescent="0.35">
@@ -3847,42 +3852,42 @@
     </row>
     <row r="383" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B383" s="16" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="384" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B384" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="385" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B385" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="386" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B386" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="387" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B387" s="16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="388" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B388" s="16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="389" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B389" s="16" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="390" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B390" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3922,8 +3927,9 @@
     <hyperlink ref="C303" r:id="rId33" xr:uid="{FE0D6467-E78B-4599-9202-BF40FD2B2BDD}"/>
     <hyperlink ref="C330" r:id="rId34" xr:uid="{8D01ECEB-758E-4418-9BC5-2A7896C3F34C}"/>
     <hyperlink ref="C349" r:id="rId35" xr:uid="{A1CEA8FE-2DF9-4EF3-8CC1-9B31F009191E}"/>
+    <hyperlink ref="C362" r:id="rId36" xr:uid="{9CD2F149-E227-4FC7-9279-6AF80B4FF6EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId36"/>
+  <pageSetup orientation="portrait" r:id="rId37"/>
 </worksheet>
 </file>
--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5F10C37138A14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="688" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44740330-921F-489F-9DA2-325C4D79A2D2}"/>
+  <xr:revisionPtr revIDLastSave="694" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96ABB39C-CFB4-430C-B10A-41371D9B5D99}"/>
   <bookViews>
-    <workbookView xWindow="2976" yWindow="1488" windowWidth="17280" windowHeight="9420" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="4020" yWindow="2532" windowWidth="17280" windowHeight="9420" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="386">
   <si>
     <t>Date</t>
   </si>
@@ -1281,12 +1281,36 @@
   <si>
     <t>Assignment 40</t>
   </si>
+  <si>
+    <t>Session Method</t>
+  </si>
+  <si>
+    <t>1.what is session method?</t>
+  </si>
+  <si>
+    <t>2.Why and when we go for call transaction and session method ?</t>
+  </si>
+  <si>
+    <t>3.Differnce between session method and call transaction method?</t>
+  </si>
+  <si>
+    <t>5.try to upload some record which is already created and upload using session method?</t>
+  </si>
+  <si>
+    <t>6.explore all 3 session method funtion module?</t>
+  </si>
+  <si>
+    <t>7.what is use of keep,dest,group,holdate in bdc_open_group?</t>
+  </si>
+  <si>
+    <t>4.what is advantage of session method over call transaction?</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1509,6 +1533,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1549,7 +1581,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1643,6 +1675,7 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1956,9 +1989,36 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{D6E18F14-8040-4D8C-B947-4F786859EBD0}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;e2f7922a-27c5-4481-b965-cca2a582c21d&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E390"/>
+  <dimension ref="A2:E400"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -3888,6 +3948,46 @@
     <row r="390" spans="2:2" ht="18" x14ac:dyDescent="0.35">
       <c r="B390" s="16" t="s">
         <v>376</v>
+      </c>
+    </row>
+    <row r="393" spans="2:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B393" s="45" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="394" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B394" s="29" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="395" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B395" s="29" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="396" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B396" s="29" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="397" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B397" s="29" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="398" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B398" s="29" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="399" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B399" s="29" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="400" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B400" s="29" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5F10C37138A14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="694" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96ABB39C-CFB4-430C-B10A-41371D9B5D99}"/>
+  <xr:revisionPtr revIDLastSave="703" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9724749B-55FC-4940-A3CE-356938B62341}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="2532" windowWidth="17280" windowHeight="9420" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="4368" yWindow="2880" windowWidth="17280" windowHeight="9420" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="411">
   <si>
     <t>Date</t>
   </si>
@@ -1305,12 +1305,87 @@
   <si>
     <t>4.what is advantage of session method over call transaction?</t>
   </si>
+  <si>
+    <t>Assignment-45 -  BDC  (application server)</t>
+  </si>
+  <si>
+    <t>1.Practice both upload to AL11 and download form AL11 ?</t>
+  </si>
+  <si>
+    <t>2.upload the data with proper format and alignment?</t>
+  </si>
+  <si>
+    <t>3.Upload the data from legacy system to SAP system TO ztable( take 2 to 3 fields)?</t>
+  </si>
+  <si>
+    <t>4.Download the data from SAP system to legacy system into word file and excel file from ztable?</t>
+  </si>
+  <si>
+    <t>Assignment-46 -  BAPI</t>
+  </si>
+  <si>
+    <t>1.What is the use of BAPI?</t>
+  </si>
+  <si>
+    <t>2.Difference between RFC and BAPI?</t>
+  </si>
+  <si>
+    <t>3. Difference between BAPI and BDC?</t>
+  </si>
+  <si>
+    <t>4. What is BOR?</t>
+  </si>
+  <si>
+    <t>5. What is SW01?</t>
+  </si>
+  <si>
+    <t>6. Why we go for BAPI?</t>
+  </si>
+  <si>
+    <t>Assignment-47 -  BAPI</t>
+  </si>
+  <si>
+    <t>1.Create 5 to 6 material in single shot using BAPI (both excel sheet and flat file)?</t>
+  </si>
+  <si>
+    <t>2.Using of clear buffer?</t>
+  </si>
+  <si>
+    <t>3.Use of BAPI_TRANSACTION_COMMIT and BAPI_TRANSACTION_ROLLBACK?</t>
+  </si>
+  <si>
+    <t>4.How to find BAPI?</t>
+  </si>
+  <si>
+    <t>Assignment-48 -  BAPI (custome bapi)</t>
+  </si>
+  <si>
+    <t>2. Do curd operation using BAPI in MPP (use custom table)?</t>
+  </si>
+  <si>
+    <t>3. Call created ZBAPI in SE38?</t>
+  </si>
+  <si>
+    <t>4. Go through the standard BAPI's?</t>
+  </si>
+  <si>
+    <t>5. How to find BAPI?</t>
+  </si>
+  <si>
+    <t>6. what is BAPI transaction commit and rollback and its difference?</t>
+  </si>
+  <si>
+    <t>Assignment-49 -  BAPI</t>
+  </si>
+  <si>
+    <t>No Assignment on Extension BAPI</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1541,6 +1616,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1581,7 +1663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1676,6 +1758,16 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1692,6 +1784,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2018,7 +2114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E400"/>
+  <dimension ref="A2:E434"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -3988,6 +4084,149 @@
     <row r="400" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B400" s="29" t="s">
         <v>384</v>
+      </c>
+    </row>
+    <row r="403" spans="2:2" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="B403" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="404" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B404" s="29" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="405" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B405" s="29" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="406" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B406" s="29" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="407" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B407" s="29" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="409" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B409" s="29"/>
+    </row>
+    <row r="410" spans="2:2" s="23" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B410" s="49" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="411" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B411" s="35"/>
+    </row>
+    <row r="412" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B412" s="29" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="413" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B413" s="46" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="414" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B414" s="29" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="415" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B415" s="29" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="416" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B416" s="29" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="417" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B417" s="29" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="418" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B418" s="29"/>
+    </row>
+    <row r="419" spans="2:2" s="23" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B419" s="49" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="420" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B420" s="47" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="421" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B421" s="47" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="422" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B422" s="47" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="423" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B423" s="47" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B424" s="47"/>
+    </row>
+    <row r="425" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B425" s="29"/>
+    </row>
+    <row r="426" spans="2:2" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B426" s="31" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="427" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B427" s="48" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="428" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B428" s="29" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="429" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B429" s="29" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="430" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B430" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="431" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B431" s="29" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="432" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B432" s="29"/>
+    </row>
+    <row r="433" spans="2:2" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B433" s="31" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="434" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B434" s="29" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>

--- a/Krishna Assignment.xlsx
+++ b/Krishna Assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5F10C37138A14469/Desktop/SAP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="703" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9724749B-55FC-4940-A3CE-356938B62341}"/>
+  <xr:revisionPtr revIDLastSave="719" documentId="8_{C4CB7184-34CC-4D88-B47A-A2840B42DD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{257B4013-A8E6-4C0A-914A-F07ED626FDDB}"/>
   <bookViews>
-    <workbookView xWindow="4368" yWindow="2880" windowWidth="17280" windowHeight="9420" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
+    <workbookView xWindow="4020" yWindow="2532" windowWidth="17280" windowHeight="9420" xr2:uid="{26A7549B-DA9D-4851-B6BF-1D9C48768FDE}"/>
   </bookViews>
   <sheets>
     <sheet name="ABAP" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="414">
   <si>
     <t>Date</t>
   </si>
@@ -1379,6 +1379,15 @@
   </si>
   <si>
     <t>No Assignment on Extension BAPI</t>
+  </si>
+  <si>
+    <t>7. Rules to create BAPI.</t>
+  </si>
+  <si>
+    <t>Assignment 46</t>
+  </si>
+  <si>
+    <t>Assignment 45</t>
   </si>
 </sst>
 </file>
@@ -1786,10 +1795,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2114,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{970B57CD-2E87-4C38-BB7E-7DC8579D2EE2}">
-  <dimension ref="A2:E434"/>
+  <dimension ref="A2:E435"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -4086,63 +4091,69 @@
         <v>384</v>
       </c>
     </row>
-    <row r="403" spans="2:2" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="403" spans="2:3" s="23" customFormat="1" ht="23.4" x14ac:dyDescent="0.3">
       <c r="B403" s="6" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="404" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="C403" s="32" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="404" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B404" s="29" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="405" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="405" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B405" s="29" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="406" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="406" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B406" s="29" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="407" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="407" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B407" s="29" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="409" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="409" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B409" s="29"/>
     </row>
-    <row r="410" spans="2:2" s="23" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="410" spans="2:3" s="23" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B410" s="49" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="411" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="C410" s="32" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="411" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B411" s="35"/>
     </row>
-    <row r="412" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="412" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B412" s="29" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="413" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="413" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B413" s="46" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="414" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="414" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B414" s="29" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="415" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="415" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B415" s="29" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="416" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="416" spans="2:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B416" s="29" t="s">
         <v>396</v>
       </c>
@@ -4153,79 +4164,84 @@
       </c>
     </row>
     <row r="418" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B418" s="29"/>
-    </row>
-    <row r="419" spans="2:2" s="23" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B419" s="49" t="s">
+      <c r="B418" s="29" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="419" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B419" s="29"/>
+    </row>
+    <row r="420" spans="2:2" s="23" customFormat="1" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B420" s="49" t="s">
         <v>398</v>
-      </c>
-    </row>
-    <row r="420" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B420" s="47" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="421" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B421" s="47" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="422" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B422" s="47" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="423" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B423" s="47" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="424" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B424" s="47" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="424" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B424" s="47"/>
-    </row>
     <row r="425" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B425" s="29"/>
-    </row>
-    <row r="426" spans="2:2" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B426" s="31" t="s">
+      <c r="B425" s="47"/>
+    </row>
+    <row r="426" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B426" s="29"/>
+    </row>
+    <row r="427" spans="2:2" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B427" s="31" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="427" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B427" s="48" t="s">
+    <row r="428" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B428" s="48" t="s">
         <v>404</v>
-      </c>
-    </row>
-    <row r="428" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B428" s="29" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="429" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B429" s="29" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="430" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B430" s="29" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="431" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B431" s="29" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="432" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B432" s="29" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="432" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B432" s="29"/>
-    </row>
-    <row r="433" spans="2:2" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B433" s="31" t="s">
+    <row r="433" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B433" s="29"/>
+    </row>
+    <row r="434" spans="2:2" s="23" customFormat="1" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B434" s="31" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="434" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B434" s="29" t="s">
+    <row r="435" spans="2:2" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="B435" s="29" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4267,8 +4283,10 @@
     <hyperlink ref="C330" r:id="rId34" xr:uid="{8D01ECEB-758E-4418-9BC5-2A7896C3F34C}"/>
     <hyperlink ref="C349" r:id="rId35" xr:uid="{A1CEA8FE-2DF9-4EF3-8CC1-9B31F009191E}"/>
     <hyperlink ref="C362" r:id="rId36" xr:uid="{9CD2F149-E227-4FC7-9279-6AF80B4FF6EA}"/>
+    <hyperlink ref="C410" r:id="rId37" xr:uid="{CB7D85E7-F797-4F91-9E70-F04729A22050}"/>
+    <hyperlink ref="C403" r:id="rId38" xr:uid="{2358BE53-6989-4E83-AD32-0702B8B4A223}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId37"/>
+  <pageSetup orientation="portrait" r:id="rId39"/>
 </worksheet>
 </file>